--- a/data/presentation_requests.xlsx
+++ b/data/presentation_requests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,6 +569,110 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>Accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TP012345</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Test Student</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Demo Lecturer 1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Demo Lecturer 2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>01:00 PM - 02:00 PM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TP015826</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Test Student 4</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Demo Lecturer 1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Demo Lecturer 2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>11:00 AM - 12:00 PM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Pending</t>
         </is>
       </c>
     </row>

--- a/data/presentation_requests.xlsx
+++ b/data/presentation_requests.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,206 +471,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TP456789</t>
+          <t>TP083880</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Test Student 2</t>
+          <t>Yoon</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Demo Lecturer 3</t>
+          <t>HEMA LATHA A/P KRISHNA NAIR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Demo Lecturer 1</t>
+          <t>DR. JULIA BINTI JUREMI</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11:00 AM - 12:00 PM</t>
+          <t>10:00 AM - 11:00 AM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Accepted</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TP012345</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Test Student</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>10:00 AM - 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Rejected</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TP012345</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Test Student</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 2</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>01:00 PM - 02:00 PM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Scheduled</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Accepted</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TP015826</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Test Student 4</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Demo Lecturer 2</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>11:00 AM - 12:00 PM</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
         <is>
           <t>Pending</t>
         </is>
